--- a/tables/qF46/relational_division_tables.xlsx
+++ b/tables/qF46/relational_division_tables.xlsx
@@ -4,7 +4,7 @@
   <fileVersion lastEdited="4" lowestEdited="4" rupBuild="3820"/>
   <workbookPr date1904="0"/>
   <bookViews>
-    <workbookView activeTab="0" windowWidth="14920" windowHeight="7700"/>
+    <workbookView activeTab="0" windowWidth="19200" windowHeight="8330"/>
   </bookViews>
   <sheets>
     <sheet name="Relational_Division" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -93,8 +93,8 @@
       <b val="1"/>
       <i val="0"/>
       <u val="none"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Times New Roman"/>
+      <color rgb="FF000000"/>
+      <name val="Sans"/>
       <vertAlign val="baseline"/>
       <sz val="11"/>
       <strike val="0"/>
@@ -119,6 +119,16 @@
       <sz val="16"/>
       <strike val="0"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <u val="none"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <vertAlign val="baseline"/>
+      <sz val="11"/>
+      <strike val="0"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -135,7 +145,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF000000"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF374151"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF374151"/>
         <bgColor rgb="FF374151"/>
       </patternFill>
     </fill>
@@ -145,20 +167,8 @@
         <bgColor rgb="FFE5E7EB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3F4F6"/>
-        <bgColor rgb="FFF3F4F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF374151"/>
-        <bgColor rgb="FF374151"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border diagonalUp="0" diagonalDown="0">
       <left style="none">
         <color rgb="FFC7C7C7"/>
@@ -171,6 +181,118 @@
       </top>
       <bottom style="none">
         <color rgb="FFC7C7C7"/>
+      </bottom>
+    </border>
+    <border diagonalUp="0" diagonalDown="0">
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FFC7C7C7"/>
+      </right>
+      <top style="none">
+        <color rgb="FFC7C7C7"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FFC7C7C7"/>
+      </bottom>
+    </border>
+    <border diagonalUp="0" diagonalDown="0">
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FFC7C7C7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border diagonalUp="0" diagonalDown="0">
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border diagonalUp="0" diagonalDown="0">
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FFC7C7C7"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FFC7C7C7"/>
+      </bottom>
+    </border>
+    <border diagonalUp="0" diagonalDown="0">
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FFC7C7C7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FFC7C7C7"/>
+      </bottom>
+    </border>
+    <border diagonalUp="0" diagonalDown="0">
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FFC7C7C7"/>
+      </bottom>
+    </border>
+    <border diagonalUp="0" diagonalDown="0">
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FFC7C7C7"/>
+      </bottom>
+    </border>
+    <border diagonalUp="0" diagonalDown="0">
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
     </border>
     <border diagonalUp="0" diagonalDown="0">
@@ -194,7 +316,7 @@
       <protection locked="1" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="18">
     <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
@@ -207,7 +329,15 @@
       <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="3" fillId="3" borderId="1" numFmtId="0" xfId="0">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="3" fillId="3" borderId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="3" fillId="3" borderId="3" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
@@ -215,7 +345,19 @@
       <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="4" fillId="5" borderId="1" numFmtId="0" xfId="0">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="4" fillId="4" borderId="4" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="4" fillId="4" borderId="5" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="4" fillId="4" borderId="6" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="3" fillId="3" borderId="7" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
@@ -223,7 +365,27 @@
       <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="3" fillId="6" borderId="1" numFmtId="0" xfId="0">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="4" fillId="4" borderId="7" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="4" fillId="4" borderId="3" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="4" fillId="4" borderId="8" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="4" fillId="4" borderId="2" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="6" fillId="5" borderId="9" numFmtId="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="4" fillId="6" borderId="9" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
@@ -258,20 +420,21 @@
           <t>R (Student, Skill)</t>
         </is>
       </c>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" spans="2:11" customHeight="1" ht="22">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:11" customHeight="1" ht="22">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="7" t="s">
         <v>3</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -281,13 +444,13 @@
       </c>
     </row>
     <row r="5" spans="2:11" customHeight="1" ht="22">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="5" t="s">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -297,78 +460,70 @@
       </c>
     </row>
     <row r="6" spans="2:11" customHeight="1" ht="22">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="10" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:11" customHeight="1" ht="22">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>÷</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="E7" s="11"/>
+      <c r="G7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="s">
+      <c r="I7" s="11"/>
+      <c r="K7" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="2:11" customHeight="1" ht="22">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="14" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:11" customHeight="1" ht="22">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="2:11" customHeight="1" ht="22">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="9" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="2:11" customHeight="1" ht="22">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="13" t="s">
         <v>5</v>
       </c>
     </row>
@@ -401,74 +556,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="17" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="17" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="17" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="17" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="17" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="17" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="17" t="s">
         <v>5</v>
       </c>
     </row>
@@ -497,22 +652,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="17" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="17" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="17" t="s">
         <v>5</v>
       </c>
     </row>
@@ -541,17 +696,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="17" t="s">
         <v>7</v>
       </c>
     </row>
